--- a/TEST DATI SAMPLE.xlsx
+++ b/TEST DATI SAMPLE.xlsx
@@ -1,22 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fraca\Desktop\sales\forecast_refactored\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61BAF531-BCA7-49E1-835B-1F6C432B6D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3760" yWindow="3760" windowWidth="28800" windowHeight="15410" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="VOLUMI" sheetId="1" r:id="rId1"/>
-    <sheet name="PREZZOMODA" sheetId="2" r:id="rId2"/>
+    <sheet r:id="rId1" sheetId="1" name="VOLUMI"/>
+    <sheet r:id="rId2" sheetId="2" name="PREZZOMODA"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -272,11 +266,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="\$#,##0.00000000000_);\(\$#,##0.00000000000\)"/>
+    <numFmt numFmtId="164" formatCode="$#,##0.00000000000_);($#,##0.00000000000)"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -286,14 +280,20 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFff0000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -324,41 +324,47 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+  <cellXfs count="11">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -369,10 +375,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -410,71 +416,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -502,7 +508,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -525,11 +531,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -538,13 +544,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -554,7 +560,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -563,7 +569,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -572,7 +578,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -580,10 +586,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -648,1143 +654,1360 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:BV7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="8" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="53" width="9" style="7" bestFit="1" customWidth="1"/>
-    <col min="54" max="62" width="8" style="7" bestFit="1" customWidth="1"/>
-    <col min="63" max="74" width="9" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="7" width="9.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="10" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="10" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="10" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="10" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="10" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="10" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="10" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="10" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="10" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="27" max="27" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="28" max="28" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="29" max="29" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="30" max="30" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="31" max="31" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="32" max="32" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="33" max="33" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="34" max="34" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="35" max="35" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="36" max="36" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="37" max="37" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="38" max="38" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="39" max="39" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="40" max="40" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="41" max="41" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="42" max="42" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="43" max="43" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="44" max="44" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="45" max="45" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="46" max="46" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="47" max="47" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="48" max="48" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="49" max="49" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="50" max="50" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="51" max="51" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="52" max="52" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="53" max="53" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="54" max="54" style="10" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="55" max="55" style="10" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="56" max="56" style="10" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="57" max="57" style="10" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="58" max="58" style="10" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="59" max="59" style="10" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="60" max="60" style="10" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="61" max="61" style="10" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="62" max="62" style="10" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="63" max="63" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="64" max="64" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="65" max="65" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="66" max="66" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="67" max="67" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="68" max="68" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="69" max="69" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="70" max="70" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="71" max="71" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="72" max="72" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="73" max="73" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="74" max="74" style="10" width="9.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:74" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="9"/>
+      <c r="AC1" s="9"/>
+      <c r="AD1" s="9"/>
+      <c r="AE1" s="9"/>
+      <c r="AF1" s="9"/>
+      <c r="AG1" s="9"/>
+      <c r="AH1" s="9"/>
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="9"/>
+      <c r="AK1" s="9"/>
+      <c r="AL1" s="9"/>
+      <c r="AM1" s="9"/>
+      <c r="AN1" s="9"/>
+      <c r="AO1" s="9"/>
+      <c r="AP1" s="9"/>
+      <c r="AQ1" s="9"/>
+      <c r="AR1" s="9"/>
+      <c r="AS1" s="9"/>
+      <c r="AT1" s="9"/>
+      <c r="AU1" s="9"/>
+      <c r="AV1" s="9"/>
+      <c r="AW1" s="9"/>
+      <c r="AX1" s="9"/>
+      <c r="AY1" s="9"/>
+      <c r="AZ1" s="9"/>
+      <c r="BA1" s="9"/>
+      <c r="BB1" s="9"/>
+      <c r="BC1" s="9"/>
+      <c r="BD1" s="9"/>
+      <c r="BE1" s="9"/>
+      <c r="BF1" s="9"/>
+      <c r="BG1" s="9"/>
+      <c r="BH1" s="9"/>
+      <c r="BI1" s="9"/>
+      <c r="BJ1" s="9"/>
+      <c r="BK1" s="9"/>
+      <c r="BL1" s="9"/>
+      <c r="BM1" s="9"/>
+      <c r="BN1" s="9"/>
+      <c r="BO1" s="9"/>
+      <c r="BP1" s="9"/>
+      <c r="BQ1" s="9"/>
+      <c r="BR1" s="9"/>
+      <c r="BS1" s="9"/>
+      <c r="BT1" s="9"/>
+      <c r="BU1" s="9"/>
+      <c r="BV1" s="9"/>
     </row>
-    <row r="2" spans="1:74" ht="18.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:74" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
+      <c r="AC2" s="9"/>
+      <c r="AD2" s="9"/>
+      <c r="AE2" s="9"/>
+      <c r="AF2" s="9"/>
+      <c r="AG2" s="9"/>
+      <c r="AH2" s="9"/>
+      <c r="AI2" s="9"/>
+      <c r="AJ2" s="9"/>
+      <c r="AK2" s="9"/>
+      <c r="AL2" s="9"/>
+      <c r="AM2" s="9"/>
+      <c r="AN2" s="9"/>
+      <c r="AO2" s="9"/>
+      <c r="AP2" s="9"/>
+      <c r="AQ2" s="9"/>
+      <c r="AR2" s="9"/>
+      <c r="AS2" s="9"/>
+      <c r="AT2" s="9"/>
+      <c r="AU2" s="9"/>
+      <c r="AV2" s="9"/>
+      <c r="AW2" s="9"/>
+      <c r="AX2" s="9"/>
+      <c r="AY2" s="9"/>
+      <c r="AZ2" s="9"/>
+      <c r="BA2" s="9"/>
+      <c r="BB2" s="9"/>
+      <c r="BC2" s="9"/>
+      <c r="BD2" s="9"/>
+      <c r="BE2" s="9"/>
+      <c r="BF2" s="9"/>
+      <c r="BG2" s="9"/>
+      <c r="BH2" s="9"/>
+      <c r="BI2" s="9"/>
+      <c r="BJ2" s="9"/>
+      <c r="BK2" s="9"/>
+      <c r="BL2" s="9"/>
+      <c r="BM2" s="9"/>
+      <c r="BN2" s="9"/>
+      <c r="BO2" s="9"/>
+      <c r="BP2" s="9"/>
+      <c r="BQ2" s="9"/>
+      <c r="BR2" s="9"/>
+      <c r="BS2" s="9"/>
+      <c r="BT2" s="9"/>
+      <c r="BU2" s="9"/>
+      <c r="BV2" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="Q3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="R3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="S3" s="7" t="s">
+      <c r="S3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="T3" s="7" t="s">
+      <c r="T3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="U3" s="7" t="s">
+      <c r="U3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="V3" s="7" t="s">
+      <c r="V3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="W3" s="7" t="s">
+      <c r="W3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="X3" s="7" t="s">
+      <c r="X3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="Y3" s="7" t="s">
+      <c r="Y3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="Z3" s="7" t="s">
+      <c r="Z3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AA3" s="7" t="s">
+      <c r="AA3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AB3" s="7" t="s">
+      <c r="AB3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AC3" s="7" t="s">
+      <c r="AC3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AD3" s="7" t="s">
+      <c r="AD3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AE3" s="7" t="s">
+      <c r="AE3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AF3" s="7" t="s">
+      <c r="AF3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AG3" s="7" t="s">
+      <c r="AG3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AH3" s="7" t="s">
+      <c r="AH3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AI3" s="7" t="s">
+      <c r="AI3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AJ3" s="7" t="s">
+      <c r="AJ3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AK3" s="7" t="s">
+      <c r="AK3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AL3" s="7" t="s">
+      <c r="AL3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AM3" s="7" t="s">
+      <c r="AM3" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="AN3" s="7" t="s">
+      <c r="AN3" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="AO3" s="7" t="s">
+      <c r="AO3" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AP3" s="7" t="s">
+      <c r="AP3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="AQ3" s="7" t="s">
+      <c r="AQ3" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="AR3" s="7" t="s">
+      <c r="AR3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="AS3" s="7" t="s">
+      <c r="AS3" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="AT3" s="7" t="s">
+      <c r="AT3" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="AU3" s="7" t="s">
+      <c r="AU3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AV3" s="7" t="s">
+      <c r="AV3" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="AW3" s="7" t="s">
+      <c r="AW3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="AX3" s="7" t="s">
+      <c r="AX3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AY3" s="7" t="s">
+      <c r="AY3" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AZ3" s="7" t="s">
+      <c r="AZ3" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="BA3" s="7" t="s">
+      <c r="BA3" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="BB3" s="7" t="s">
+      <c r="BB3" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="BC3" s="7" t="s">
+      <c r="BC3" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="BD3" s="7" t="s">
+      <c r="BD3" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="BE3" s="7" t="s">
+      <c r="BE3" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="BF3" s="7" t="s">
+      <c r="BF3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="BG3" s="7" t="s">
+      <c r="BG3" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="BH3" s="7" t="s">
+      <c r="BH3" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="BI3" s="7" t="s">
+      <c r="BI3" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="BJ3" s="7" t="s">
+      <c r="BJ3" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="BK3" s="7" t="s">
+      <c r="BK3" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="BL3" s="7" t="s">
+      <c r="BL3" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="BM3" s="7" t="s">
+      <c r="BM3" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="BN3" s="7" t="s">
+      <c r="BN3" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="BO3" s="7" t="s">
+      <c r="BO3" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="BP3" s="7" t="s">
+      <c r="BP3" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="BQ3" s="7" t="s">
+      <c r="BQ3" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="BR3" s="7" t="s">
+      <c r="BR3" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="BS3" s="7" t="s">
+      <c r="BS3" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="BT3" s="7" t="s">
+      <c r="BT3" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="BU3" s="7" t="s">
+      <c r="BU3" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="BV3" s="7" t="s">
+      <c r="BV3" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:74" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3">
-        <v>0</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3">
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
         <v>2</v>
       </c>
-      <c r="E4" s="3">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3">
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
         <v>340</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <v>1240</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="2">
         <v>2374</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="2">
         <v>2700</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="2">
         <v>3330</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="2">
         <v>2946</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="2">
         <v>2796</v>
       </c>
-      <c r="M4" s="3">
+      <c r="M4" s="2">
         <v>3216</v>
       </c>
-      <c r="N4" s="3">
+      <c r="N4" s="2">
         <v>2768</v>
       </c>
-      <c r="O4" s="3">
+      <c r="O4" s="2">
         <v>2934</v>
       </c>
-      <c r="P4" s="3">
+      <c r="P4" s="2">
         <v>2842</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="Q4" s="2">
         <v>2894</v>
       </c>
-      <c r="R4" s="3">
+      <c r="R4" s="2">
         <v>2526</v>
       </c>
-      <c r="S4" s="3">
+      <c r="S4" s="2">
         <v>2742</v>
       </c>
-      <c r="T4" s="3">
+      <c r="T4" s="2">
         <v>3272</v>
       </c>
-      <c r="U4" s="3">
+      <c r="U4" s="2">
         <v>3950</v>
       </c>
-      <c r="V4" s="3">
+      <c r="V4" s="2">
         <v>3168</v>
       </c>
-      <c r="W4" s="3">
+      <c r="W4" s="2">
         <v>2658</v>
       </c>
-      <c r="X4" s="3">
+      <c r="X4" s="2">
         <v>2610</v>
       </c>
-      <c r="Y4" s="3">
+      <c r="Y4" s="2">
         <v>3094</v>
       </c>
-      <c r="Z4" s="3">
+      <c r="Z4" s="2">
         <v>2958</v>
       </c>
-      <c r="AA4" s="3">
+      <c r="AA4" s="2">
         <v>2522</v>
       </c>
-      <c r="AB4" s="3">
+      <c r="AB4" s="2">
         <v>2922</v>
       </c>
-      <c r="AC4" s="3">
+      <c r="AC4" s="2">
         <v>3590</v>
       </c>
-      <c r="AD4" s="3">
+      <c r="AD4" s="2">
         <v>4086</v>
       </c>
-      <c r="AE4" s="3">
+      <c r="AE4" s="2">
         <v>3668</v>
       </c>
-      <c r="AF4" s="3">
+      <c r="AF4" s="2">
         <v>3616</v>
       </c>
-      <c r="AG4" s="3">
+      <c r="AG4" s="2">
         <v>2772</v>
       </c>
-      <c r="AH4" s="3">
+      <c r="AH4" s="2">
         <v>2476</v>
       </c>
-      <c r="AI4" s="3">
+      <c r="AI4" s="2">
         <v>1930</v>
       </c>
-      <c r="AJ4" s="3">
+      <c r="AJ4" s="2">
         <v>1734</v>
       </c>
-      <c r="AK4" s="3">
+      <c r="AK4" s="2">
         <v>1894</v>
       </c>
-      <c r="AL4" s="3">
+      <c r="AL4" s="2">
         <v>2076</v>
       </c>
-      <c r="AM4" s="3">
+      <c r="AM4" s="2">
         <v>2682</v>
       </c>
-      <c r="AN4" s="3">
+      <c r="AN4" s="2">
         <v>2714</v>
       </c>
-      <c r="AO4" s="3">
+      <c r="AO4" s="2">
         <v>2318</v>
       </c>
-      <c r="AP4" s="3">
+      <c r="AP4" s="2">
         <v>1812</v>
       </c>
-      <c r="AQ4" s="3">
+      <c r="AQ4" s="2">
         <v>1528</v>
       </c>
-      <c r="AR4" s="3">
+      <c r="AR4" s="2">
         <v>1546</v>
       </c>
-      <c r="AS4" s="3">
+      <c r="AS4" s="2">
         <v>1432</v>
       </c>
-      <c r="AT4" s="3">
+      <c r="AT4" s="2">
         <v>1570</v>
       </c>
-      <c r="AU4" s="3">
+      <c r="AU4" s="2">
         <v>1406</v>
       </c>
-      <c r="AV4" s="3">
+      <c r="AV4" s="2">
         <v>2356</v>
       </c>
-      <c r="AW4" s="3">
+      <c r="AW4" s="2">
         <v>1764</v>
       </c>
-      <c r="AX4" s="3">
+      <c r="AX4" s="2">
         <v>1964</v>
       </c>
-      <c r="AY4" s="3">
+      <c r="AY4" s="2">
         <v>3530</v>
       </c>
-      <c r="AZ4" s="3">
+      <c r="AZ4" s="2">
         <v>3040</v>
       </c>
-      <c r="BA4" s="3">
+      <c r="BA4" s="2">
         <v>2774</v>
       </c>
-      <c r="BB4" s="3">
+      <c r="BB4" s="2">
         <v>2568</v>
       </c>
-      <c r="BC4" s="3">
+      <c r="BC4" s="2">
         <v>2916</v>
       </c>
-      <c r="BD4" s="3">
+      <c r="BD4" s="2">
         <v>2492</v>
       </c>
-      <c r="BE4" s="3">
+      <c r="BE4" s="2">
         <v>1970</v>
       </c>
-      <c r="BF4" s="3">
+      <c r="BF4" s="2">
         <v>2266</v>
       </c>
-      <c r="BG4" s="3">
+      <c r="BG4" s="2">
         <v>2492</v>
       </c>
-      <c r="BH4" s="3">
+      <c r="BH4" s="2">
         <v>1906</v>
       </c>
-      <c r="BI4" s="3">
+      <c r="BI4" s="2">
         <v>1388</v>
       </c>
-      <c r="BJ4" s="3">
+      <c r="BJ4" s="2">
         <v>1308</v>
       </c>
-      <c r="BK4" s="3">
+      <c r="BK4" s="2">
         <v>1164</v>
       </c>
-      <c r="BL4" s="3">
+      <c r="BL4" s="2">
         <v>1178</v>
       </c>
-      <c r="BM4" s="3">
+      <c r="BM4" s="2">
         <v>976</v>
       </c>
-      <c r="BN4" s="3">
+      <c r="BN4" s="2">
         <v>856</v>
       </c>
-      <c r="BO4" s="3">
+      <c r="BO4" s="2">
         <v>978</v>
       </c>
-      <c r="BP4" s="3">
+      <c r="BP4" s="2">
         <v>1082</v>
       </c>
-      <c r="BQ4" s="3">
+      <c r="BQ4" s="2">
         <v>706</v>
       </c>
-      <c r="BR4" s="3">
+      <c r="BR4" s="2">
         <v>724</v>
       </c>
-      <c r="BS4" s="3">
+      <c r="BS4" s="2">
         <v>586</v>
       </c>
-      <c r="BT4" s="3">
+      <c r="BT4" s="2">
         <v>484</v>
       </c>
-      <c r="BU4" s="3">
+      <c r="BU4" s="2">
         <v>466</v>
       </c>
-      <c r="BV4" s="3">
+      <c r="BV4" s="2">
         <v>436</v>
       </c>
     </row>
-    <row r="5" spans="1:74" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>660</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>668</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>658</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>541</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>534</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>452</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <v>472</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="2">
         <v>427</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="2">
         <v>438</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="2">
         <v>406</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="2">
         <v>402</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5" s="2">
         <v>393</v>
       </c>
-      <c r="N5" s="3">
+      <c r="N5" s="2">
         <v>412</v>
       </c>
-      <c r="O5" s="3">
+      <c r="O5" s="2">
         <v>577</v>
       </c>
-      <c r="P5" s="3">
+      <c r="P5" s="2">
         <v>504</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="Q5" s="2">
         <v>613</v>
       </c>
-      <c r="R5" s="3">
+      <c r="R5" s="2">
         <v>544</v>
       </c>
-      <c r="S5" s="3">
+      <c r="S5" s="2">
         <v>488</v>
       </c>
-      <c r="T5" s="3">
+      <c r="T5" s="2">
         <v>434</v>
       </c>
-      <c r="U5" s="3">
+      <c r="U5" s="2">
         <v>489</v>
       </c>
-      <c r="V5" s="3">
+      <c r="V5" s="2">
         <v>442</v>
       </c>
-      <c r="W5" s="3">
+      <c r="W5" s="2">
         <v>389</v>
       </c>
-      <c r="X5" s="3">
+      <c r="X5" s="2">
         <v>502</v>
       </c>
-      <c r="Y5" s="3">
+      <c r="Y5" s="2">
         <v>396</v>
       </c>
-      <c r="Z5" s="3">
+      <c r="Z5" s="2">
         <v>387</v>
       </c>
-      <c r="AA5" s="3">
+      <c r="AA5" s="2">
         <v>389</v>
       </c>
-      <c r="AB5" s="3">
+      <c r="AB5" s="2">
         <v>445</v>
       </c>
-      <c r="AC5" s="3">
+      <c r="AC5" s="2">
         <v>498</v>
       </c>
-      <c r="AD5" s="3">
+      <c r="AD5" s="2">
         <v>404</v>
       </c>
-      <c r="AE5" s="3">
+      <c r="AE5" s="2">
         <v>334</v>
       </c>
-      <c r="AF5" s="3">
+      <c r="AF5" s="2">
         <v>427</v>
       </c>
-      <c r="AG5" s="3">
+      <c r="AG5" s="2">
         <v>502</v>
       </c>
-      <c r="AH5" s="3">
+      <c r="AH5" s="2">
         <v>477</v>
       </c>
-      <c r="AI5" s="3">
+      <c r="AI5" s="2">
         <v>437</v>
       </c>
-      <c r="AJ5" s="3">
+      <c r="AJ5" s="2">
         <v>397</v>
       </c>
-      <c r="AK5" s="3">
+      <c r="AK5" s="2">
         <v>391</v>
       </c>
-      <c r="AL5" s="3">
+      <c r="AL5" s="2">
         <v>521</v>
       </c>
-      <c r="AM5" s="3">
+      <c r="AM5" s="2">
         <v>385</v>
       </c>
-      <c r="AN5" s="3">
+      <c r="AN5" s="2">
         <v>297</v>
       </c>
-      <c r="AO5" s="3">
+      <c r="AO5" s="2">
         <v>253</v>
       </c>
-      <c r="AP5" s="3">
+      <c r="AP5" s="2">
         <v>209</v>
       </c>
-      <c r="AQ5" s="3">
+      <c r="AQ5" s="2">
         <v>211</v>
       </c>
-      <c r="AR5" s="3">
+      <c r="AR5" s="2">
         <v>175</v>
       </c>
-      <c r="AS5" s="3">
+      <c r="AS5" s="2">
         <v>104</v>
       </c>
-      <c r="AT5" s="3">
+      <c r="AT5" s="2">
         <v>98</v>
       </c>
-      <c r="AU5" s="3">
+      <c r="AU5" s="2">
         <v>83</v>
       </c>
-      <c r="AV5" s="3">
+      <c r="AV5" s="2">
         <v>95</v>
       </c>
-      <c r="AW5" s="3">
+      <c r="AW5" s="2">
         <v>80</v>
       </c>
-      <c r="AX5" s="3">
+      <c r="AX5" s="2">
         <v>73</v>
       </c>
-      <c r="AY5" s="3">
+      <c r="AY5" s="2">
         <v>82</v>
       </c>
-      <c r="AZ5" s="3">
+      <c r="AZ5" s="2">
         <v>115</v>
       </c>
-      <c r="BA5" s="3">
+      <c r="BA5" s="2">
         <v>88</v>
       </c>
-      <c r="BB5" s="3">
-        <v>0</v>
-      </c>
-      <c r="BC5" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD5" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE5" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF5" s="3">
-        <v>0</v>
-      </c>
-      <c r="BG5" s="3">
-        <v>0</v>
-      </c>
-      <c r="BH5" s="3">
-        <v>0</v>
-      </c>
-      <c r="BI5" s="3">
-        <v>0</v>
-      </c>
-      <c r="BJ5" s="3">
-        <v>0</v>
-      </c>
-      <c r="BK5" s="3">
-        <v>0</v>
-      </c>
-      <c r="BL5" s="3">
-        <v>0</v>
-      </c>
-      <c r="BM5" s="3">
-        <v>0</v>
-      </c>
-      <c r="BN5" s="3">
-        <v>0</v>
-      </c>
-      <c r="BO5" s="3">
-        <v>0</v>
-      </c>
-      <c r="BP5" s="3">
-        <v>0</v>
-      </c>
-      <c r="BQ5" s="3">
-        <v>0</v>
-      </c>
-      <c r="BR5" s="3">
-        <v>0</v>
-      </c>
-      <c r="BS5" s="3">
-        <v>0</v>
-      </c>
-      <c r="BT5" s="3">
-        <v>0</v>
-      </c>
-      <c r="BU5" s="3">
-        <v>0</v>
-      </c>
-      <c r="BV5" s="3">
+      <c r="BB5" s="2">
+        <v>0</v>
+      </c>
+      <c r="BC5" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD5" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE5" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF5" s="2">
+        <v>0</v>
+      </c>
+      <c r="BG5" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH5" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI5" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ5" s="2">
+        <v>0</v>
+      </c>
+      <c r="BK5" s="2">
+        <v>0</v>
+      </c>
+      <c r="BL5" s="2">
+        <v>0</v>
+      </c>
+      <c r="BM5" s="2">
+        <v>0</v>
+      </c>
+      <c r="BN5" s="2">
+        <v>0</v>
+      </c>
+      <c r="BO5" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP5" s="2">
+        <v>0</v>
+      </c>
+      <c r="BQ5" s="2">
+        <v>0</v>
+      </c>
+      <c r="BR5" s="2">
+        <v>0</v>
+      </c>
+      <c r="BS5" s="2">
+        <v>0</v>
+      </c>
+      <c r="BT5" s="2">
+        <v>0</v>
+      </c>
+      <c r="BU5" s="2">
+        <v>0</v>
+      </c>
+      <c r="BV5" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:74" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
-        <v>0</v>
-      </c>
-      <c r="C6" s="3">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3">
-        <v>0</v>
-      </c>
-      <c r="O6" s="3">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="3">
-        <v>0</v>
-      </c>
-      <c r="R6" s="3">
-        <v>0</v>
-      </c>
-      <c r="S6" s="3">
-        <v>0</v>
-      </c>
-      <c r="T6" s="3">
-        <v>0</v>
-      </c>
-      <c r="U6" s="3">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3">
-        <v>0</v>
-      </c>
-      <c r="W6" s="3">
-        <v>0</v>
-      </c>
-      <c r="X6" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="3">
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2">
+        <v>0</v>
+      </c>
+      <c r="O6" s="2">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2">
+        <v>0</v>
+      </c>
+      <c r="T6" s="2">
+        <v>0</v>
+      </c>
+      <c r="U6" s="2">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="2">
         <v>84</v>
       </c>
-      <c r="AJ6" s="3">
+      <c r="AJ6" s="2">
         <v>540</v>
       </c>
-      <c r="AK6" s="3">
+      <c r="AK6" s="2">
         <v>2412</v>
       </c>
-      <c r="AL6" s="3">
+      <c r="AL6" s="2">
         <v>3657</v>
       </c>
-      <c r="AM6" s="3">
+      <c r="AM6" s="2">
         <v>3267</v>
       </c>
-      <c r="AN6" s="3">
+      <c r="AN6" s="2">
         <v>3456</v>
       </c>
-      <c r="AO6" s="3">
+      <c r="AO6" s="2">
         <v>2763</v>
       </c>
-      <c r="AP6" s="3">
+      <c r="AP6" s="2">
         <v>3588</v>
       </c>
-      <c r="AQ6" s="3">
+      <c r="AQ6" s="2">
         <v>3852</v>
       </c>
-      <c r="AR6" s="3">
+      <c r="AR6" s="2">
         <v>3798</v>
       </c>
-      <c r="AS6" s="3">
+      <c r="AS6" s="2">
         <v>3882</v>
       </c>
-      <c r="AT6" s="3">
+      <c r="AT6" s="2">
         <v>3696</v>
       </c>
-      <c r="AU6" s="3">
+      <c r="AU6" s="2">
         <v>5067</v>
       </c>
-      <c r="AV6" s="3">
+      <c r="AV6" s="2">
         <v>4563</v>
       </c>
-      <c r="AW6" s="3">
+      <c r="AW6" s="2">
         <v>4539</v>
       </c>
-      <c r="AX6" s="3">
+      <c r="AX6" s="2">
         <v>4161</v>
       </c>
-      <c r="AY6" s="3">
+      <c r="AY6" s="2">
         <v>5535</v>
       </c>
-      <c r="AZ6" s="3">
+      <c r="AZ6" s="2">
         <v>10146</v>
       </c>
-      <c r="BA6" s="3">
+      <c r="BA6" s="2">
         <v>7494</v>
       </c>
-      <c r="BB6" s="3">
+      <c r="BB6" s="2">
         <v>4260</v>
       </c>
-      <c r="BC6" s="3">
+      <c r="BC6" s="2">
         <v>3924</v>
       </c>
-      <c r="BD6" s="3">
+      <c r="BD6" s="2">
         <v>3924</v>
       </c>
-      <c r="BE6" s="3">
+      <c r="BE6" s="2">
         <v>3315</v>
       </c>
-      <c r="BF6" s="3">
+      <c r="BF6" s="2">
         <v>3513</v>
       </c>
-      <c r="BG6" s="3">
+      <c r="BG6" s="2">
         <v>3414</v>
       </c>
-      <c r="BH6" s="3">
+      <c r="BH6" s="2">
         <v>3171</v>
       </c>
-      <c r="BI6" s="3">
+      <c r="BI6" s="2">
         <v>2400</v>
       </c>
-      <c r="BJ6" s="3">
+      <c r="BJ6" s="2">
         <v>2124</v>
       </c>
-      <c r="BK6" s="3">
+      <c r="BK6" s="2">
         <v>1809</v>
       </c>
-      <c r="BL6" s="3">
+      <c r="BL6" s="2">
         <v>1485</v>
       </c>
-      <c r="BM6" s="3">
+      <c r="BM6" s="2">
         <v>1041</v>
       </c>
-      <c r="BN6" s="3">
+      <c r="BN6" s="2">
         <v>969</v>
       </c>
-      <c r="BO6" s="3">
+      <c r="BO6" s="2">
         <v>660</v>
       </c>
-      <c r="BP6" s="3">
+      <c r="BP6" s="2">
         <v>828</v>
       </c>
-      <c r="BQ6" s="3">
+      <c r="BQ6" s="2">
         <v>717</v>
       </c>
-      <c r="BR6" s="3">
+      <c r="BR6" s="2">
         <v>384</v>
       </c>
-      <c r="BS6" s="3">
+      <c r="BS6" s="2">
         <v>378</v>
       </c>
-      <c r="BT6" s="3">
+      <c r="BT6" s="2">
         <v>291</v>
       </c>
-      <c r="BU6" s="3">
+      <c r="BU6" s="2">
         <v>210</v>
       </c>
-      <c r="BV6" s="3">
+      <c r="BV6" s="2">
         <v>159</v>
       </c>
     </row>
-    <row r="7" spans="1:74" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="3">
-        <v>0</v>
-      </c>
-      <c r="C7" s="3">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3">
-        <v>0</v>
-      </c>
-      <c r="K7" s="3">
-        <v>0</v>
-      </c>
-      <c r="L7" s="3">
-        <v>0</v>
-      </c>
-      <c r="M7" s="3">
-        <v>0</v>
-      </c>
-      <c r="N7" s="3">
-        <v>0</v>
-      </c>
-      <c r="O7" s="3">
-        <v>0</v>
-      </c>
-      <c r="P7" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="3">
-        <v>0</v>
-      </c>
-      <c r="R7" s="3">
-        <v>0</v>
-      </c>
-      <c r="S7" s="3">
-        <v>0</v>
-      </c>
-      <c r="T7" s="3">
-        <v>0</v>
-      </c>
-      <c r="U7" s="3">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3">
-        <v>0</v>
-      </c>
-      <c r="W7" s="3">
-        <v>0</v>
-      </c>
-      <c r="X7" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="3">
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0</v>
+      </c>
+      <c r="O7" s="2">
+        <v>0</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2">
+        <v>0</v>
+      </c>
+      <c r="T7" s="2">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2">
+        <v>0</v>
+      </c>
+      <c r="W7" s="2">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="2">
         <v>6</v>
       </c>
-      <c r="AD7" s="3">
+      <c r="AD7" s="2">
         <v>56</v>
       </c>
-      <c r="AE7" s="3">
+      <c r="AE7" s="2">
         <v>111</v>
       </c>
-      <c r="AF7" s="3">
+      <c r="AF7" s="2">
         <v>176</v>
       </c>
-      <c r="AG7" s="3">
+      <c r="AG7" s="2">
         <v>196</v>
       </c>
-      <c r="AH7" s="3">
+      <c r="AH7" s="2">
         <v>207</v>
       </c>
-      <c r="AI7" s="3">
+      <c r="AI7" s="2">
         <v>210</v>
       </c>
-      <c r="AJ7" s="3">
+      <c r="AJ7" s="2">
         <v>191</v>
       </c>
-      <c r="AK7" s="3">
+      <c r="AK7" s="2">
         <v>274</v>
       </c>
-      <c r="AL7" s="3">
+      <c r="AL7" s="2">
         <v>338</v>
       </c>
-      <c r="AM7" s="3">
+      <c r="AM7" s="2">
         <v>384</v>
       </c>
-      <c r="AN7" s="3">
+      <c r="AN7" s="2">
         <v>335</v>
       </c>
-      <c r="AO7" s="3">
+      <c r="AO7" s="2">
         <v>310</v>
       </c>
-      <c r="AP7" s="3">
+      <c r="AP7" s="2">
         <v>303</v>
       </c>
-      <c r="AQ7" s="3">
+      <c r="AQ7" s="2">
         <v>349</v>
       </c>
-      <c r="AR7" s="3">
+      <c r="AR7" s="2">
         <v>353</v>
       </c>
-      <c r="AS7" s="3">
+      <c r="AS7" s="2">
         <v>282</v>
       </c>
-      <c r="AT7" s="3">
+      <c r="AT7" s="2">
         <v>329</v>
       </c>
-      <c r="AU7" s="3">
+      <c r="AU7" s="2">
         <v>370</v>
       </c>
-      <c r="AV7" s="3">
+      <c r="AV7" s="2">
         <v>308</v>
       </c>
-      <c r="AW7" s="3">
+      <c r="AW7" s="2">
         <v>668</v>
       </c>
-      <c r="AX7" s="3">
+      <c r="AX7" s="2">
         <v>374</v>
       </c>
-      <c r="AY7" s="3">
+      <c r="AY7" s="2">
         <v>330</v>
       </c>
-      <c r="AZ7" s="3">
+      <c r="AZ7" s="2">
         <v>572</v>
       </c>
-      <c r="BA7" s="3">
+      <c r="BA7" s="2">
         <v>465</v>
       </c>
-      <c r="BB7" s="3">
+      <c r="BB7" s="2">
         <v>328</v>
       </c>
-      <c r="BC7" s="3">
+      <c r="BC7" s="2">
         <v>337</v>
       </c>
-      <c r="BD7" s="3">
+      <c r="BD7" s="2">
         <v>274</v>
       </c>
-      <c r="BE7" s="3">
+      <c r="BE7" s="2">
         <v>217</v>
       </c>
-      <c r="BF7" s="3">
+      <c r="BF7" s="2">
         <v>207</v>
       </c>
-      <c r="BG7" s="3">
+      <c r="BG7" s="2">
         <v>288</v>
       </c>
-      <c r="BH7" s="3">
+      <c r="BH7" s="2">
         <v>303</v>
       </c>
-      <c r="BI7" s="3">
+      <c r="BI7" s="2">
         <v>229</v>
       </c>
-      <c r="BJ7" s="3">
+      <c r="BJ7" s="2">
         <v>184</v>
       </c>
-      <c r="BK7" s="3">
+      <c r="BK7" s="2">
         <v>123</v>
       </c>
-      <c r="BL7" s="3">
+      <c r="BL7" s="2">
         <v>107</v>
       </c>
-      <c r="BM7" s="3">
+      <c r="BM7" s="2">
         <v>88</v>
       </c>
-      <c r="BN7" s="3">
+      <c r="BN7" s="2">
         <v>70</v>
       </c>
-      <c r="BO7" s="3">
+      <c r="BO7" s="2">
         <v>75</v>
       </c>
-      <c r="BP7" s="3">
+      <c r="BP7" s="2">
         <v>95</v>
       </c>
-      <c r="BQ7" s="3">
+      <c r="BQ7" s="2">
         <v>51</v>
       </c>
-      <c r="BR7" s="3">
+      <c r="BR7" s="2">
         <v>50</v>
       </c>
-      <c r="BS7" s="3">
+      <c r="BS7" s="2">
         <v>38</v>
       </c>
-      <c r="BT7" s="3">
+      <c r="BT7" s="2">
         <v>46</v>
       </c>
-      <c r="BU7" s="3">
+      <c r="BU7" s="2">
         <v>33</v>
       </c>
-      <c r="BV7" s="3">
+      <c r="BV7" s="2">
         <v>27</v>
       </c>
     </row>
@@ -1794,357 +2017,389 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:R7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="10" width="9.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="18" width="9.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="8.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2">
         <v>2024</v>
       </c>
-      <c r="C1" s="3">
+      <c r="C1" s="2">
         <v>2024</v>
       </c>
-      <c r="D1" s="3">
+      <c r="D1" s="2">
         <v>2024</v>
       </c>
-      <c r="E1" s="3">
+      <c r="E1" s="2">
         <v>2024</v>
       </c>
-      <c r="F1" s="3">
+      <c r="F1" s="2">
         <v>2024</v>
       </c>
-      <c r="G1" s="3">
+      <c r="G1" s="2">
         <v>2024</v>
       </c>
-      <c r="H1" s="3">
+      <c r="H1" s="2">
         <v>2024</v>
       </c>
-      <c r="I1" s="3">
+      <c r="I1" s="2">
         <v>2024</v>
       </c>
-      <c r="J1" s="3">
+      <c r="J1" s="2">
         <v>2024</v>
       </c>
-      <c r="K1" s="3">
+      <c r="K1" s="2">
         <v>2024</v>
       </c>
-      <c r="L1" s="3">
+      <c r="L1" s="2">
         <v>2024</v>
       </c>
-      <c r="M1" s="3">
+      <c r="M1" s="2">
         <v>2024</v>
       </c>
-      <c r="N1" s="3">
+      <c r="N1" s="2">
         <v>2025</v>
       </c>
-      <c r="O1" s="3">
+      <c r="O1" s="2">
         <v>2025</v>
       </c>
-      <c r="P1" s="3">
+      <c r="P1" s="2">
         <v>2025</v>
       </c>
-      <c r="Q1" s="3">
+      <c r="Q1" s="2">
         <v>2025</v>
       </c>
-      <c r="R1" s="3">
+      <c r="R1" s="2">
         <v>2025</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="2">
         <v>1</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <v>2</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <v>3</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <v>4</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <v>5</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <v>6</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="2">
         <v>7</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="2">
         <v>8</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="2">
         <v>9</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="2">
         <v>10</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="2">
         <v>11</v>
       </c>
-      <c r="M2" s="3">
+      <c r="M2" s="2">
         <v>12</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="2">
         <v>1</v>
       </c>
-      <c r="O2" s="3">
+      <c r="O2" s="2">
         <v>2</v>
       </c>
-      <c r="P2" s="3">
+      <c r="P2" s="2">
         <v>3</v>
       </c>
-      <c r="Q2" s="3">
+      <c r="Q2" s="2">
         <v>4</v>
       </c>
-      <c r="R2" s="3">
+      <c r="R2" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4">
-        <v>0</v>
-      </c>
-      <c r="C3" s="4">
+      <c r="B3" s="3">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3">
         <v>238</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <v>238</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="3">
         <v>238</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="3">
         <v>218</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="3">
         <v>218</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="3">
         <v>230</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="3">
         <v>230</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="3">
         <v>218</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="3">
         <v>238</v>
       </c>
-      <c r="L3" s="4">
+      <c r="L3" s="3">
         <v>198</v>
       </c>
-      <c r="M3" s="4">
+      <c r="M3" s="3">
         <v>210</v>
       </c>
-      <c r="N3" s="4">
+      <c r="N3" s="3">
         <v>218</v>
       </c>
-      <c r="O3" s="4">
+      <c r="O3" s="3">
         <v>218</v>
       </c>
-      <c r="P3" s="4">
+      <c r="P3" s="3">
         <v>218</v>
       </c>
-      <c r="Q3" s="4">
+      <c r="Q3" s="3">
         <v>226</v>
       </c>
-      <c r="R3" s="4">
+      <c r="R3" s="3">
         <v>226</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>278</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <v>278</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>278</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="3">
         <v>258</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="3">
         <v>258</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="3">
         <v>258</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="3">
         <v>258</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="3">
         <v>258</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="3">
         <v>258</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="P4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="Q4" s="5" t="s">
+      <c r="Q4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="R4" s="5" t="s">
+      <c r="R4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="4">
-        <v>0</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4">
-        <v>0</v>
-      </c>
-      <c r="F5" s="4">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4">
-        <v>0</v>
-      </c>
-      <c r="I5" s="4">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4">
+      <c r="B5" s="3">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3">
         <v>448</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="3">
         <v>398</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="3">
         <v>398</v>
       </c>
-      <c r="M5" s="4">
+      <c r="M5" s="3">
         <v>398</v>
       </c>
-      <c r="N5" s="4">
+      <c r="N5" s="3">
         <v>398</v>
       </c>
-      <c r="O5" s="4">
+      <c r="O5" s="3">
         <v>398</v>
       </c>
-      <c r="P5" s="4">
+      <c r="P5" s="3">
         <v>398</v>
       </c>
-      <c r="Q5" s="4">
+      <c r="Q5" s="3">
         <v>398</v>
       </c>
-      <c r="R5" s="4">
+      <c r="R5" s="3">
         <v>398</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="4">
-        <v>0</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4">
-        <v>0</v>
-      </c>
-      <c r="H6" s="4">
-        <v>0</v>
-      </c>
-      <c r="I6" s="4">
-        <v>0</v>
-      </c>
-      <c r="J6" s="6">
+      <c r="B6" s="3">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
         <v>598</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="5">
         <v>598</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="5">
         <v>518</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="5">
         <v>538</v>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="5">
         <v>530</v>
       </c>
-      <c r="O6" s="6">
+      <c r="O6" s="5">
         <v>578</v>
       </c>
-      <c r="P6" s="6">
+      <c r="P6" s="5">
         <v>598</v>
       </c>
-      <c r="Q6" s="6">
+      <c r="Q6" s="5">
         <v>598</v>
       </c>
-      <c r="R6" s="5" t="s">
+      <c r="R6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="1"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TEST DATI SAMPLE.xlsx
+++ b/TEST DATI SAMPLE.xlsx
@@ -270,7 +270,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0.00000000000_);($#,##0.00000000000)"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -288,12 +288,6 @@
       <sz val="11"/>
       <color rgb="FFff0000"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -324,7 +318,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -341,16 +335,10 @@
     <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -661,235 +649,235 @@
   <dimension ref="A1:BV7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="9.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="10" width="8.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="10" width="8.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="10" width="8.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="10" width="8.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="10" width="8.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="10" width="8.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="10" width="8.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="10" width="8.005" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="10" width="8.005" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="27" max="27" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="28" max="28" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="29" max="29" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="30" max="30" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="31" max="31" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="32" max="32" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="33" max="33" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="34" max="34" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="35" max="35" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="36" max="36" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="37" max="37" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="38" max="38" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="39" max="39" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="40" max="40" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="41" max="41" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="42" max="42" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="43" max="43" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="44" max="44" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="45" max="45" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="46" max="46" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="47" max="47" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="48" max="48" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="49" max="49" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="50" max="50" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="51" max="51" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="52" max="52" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="53" max="53" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="54" max="54" style="10" width="8.005" customWidth="1" bestFit="1"/>
-    <col min="55" max="55" style="10" width="8.005" customWidth="1" bestFit="1"/>
-    <col min="56" max="56" style="10" width="8.005" customWidth="1" bestFit="1"/>
-    <col min="57" max="57" style="10" width="8.005" customWidth="1" bestFit="1"/>
-    <col min="58" max="58" style="10" width="8.005" customWidth="1" bestFit="1"/>
-    <col min="59" max="59" style="10" width="8.005" customWidth="1" bestFit="1"/>
-    <col min="60" max="60" style="10" width="8.005" customWidth="1" bestFit="1"/>
-    <col min="61" max="61" style="10" width="8.005" customWidth="1" bestFit="1"/>
-    <col min="62" max="62" style="10" width="8.005" customWidth="1" bestFit="1"/>
-    <col min="63" max="63" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="64" max="64" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="65" max="65" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="66" max="66" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="67" max="67" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="68" max="68" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="69" max="69" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="70" max="70" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="71" max="71" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="72" max="72" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="73" max="73" style="10" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="74" max="74" style="10" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="6" width="9.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="8" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="8" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="8" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="8" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="27" max="27" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="28" max="28" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="29" max="29" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="30" max="30" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="31" max="31" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="32" max="32" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="33" max="33" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="34" max="34" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="35" max="35" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="36" max="36" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="37" max="37" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="38" max="38" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="39" max="39" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="40" max="40" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="41" max="41" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="42" max="42" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="43" max="43" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="44" max="44" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="45" max="45" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="46" max="46" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="47" max="47" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="48" max="48" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="49" max="49" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="50" max="50" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="51" max="51" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="52" max="52" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="53" max="53" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="54" max="54" style="8" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="55" max="55" style="8" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="56" max="56" style="8" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="57" max="57" style="8" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="58" max="58" style="8" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="59" max="59" style="8" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="60" max="60" style="8" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="61" max="61" style="8" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="62" max="62" style="8" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="63" max="63" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="64" max="64" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="65" max="65" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="66" max="66" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="67" max="67" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="68" max="68" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="69" max="69" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="70" max="70" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="71" max="71" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="72" max="72" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="73" max="73" style="8" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="74" max="74" style="8" width="9.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="9"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="9"/>
-      <c r="X1" s="9"/>
-      <c r="Y1" s="9"/>
-      <c r="Z1" s="9"/>
-      <c r="AA1" s="9"/>
-      <c r="AB1" s="9"/>
-      <c r="AC1" s="9"/>
-      <c r="AD1" s="9"/>
-      <c r="AE1" s="9"/>
-      <c r="AF1" s="9"/>
-      <c r="AG1" s="9"/>
-      <c r="AH1" s="9"/>
-      <c r="AI1" s="9"/>
-      <c r="AJ1" s="9"/>
-      <c r="AK1" s="9"/>
-      <c r="AL1" s="9"/>
-      <c r="AM1" s="9"/>
-      <c r="AN1" s="9"/>
-      <c r="AO1" s="9"/>
-      <c r="AP1" s="9"/>
-      <c r="AQ1" s="9"/>
-      <c r="AR1" s="9"/>
-      <c r="AS1" s="9"/>
-      <c r="AT1" s="9"/>
-      <c r="AU1" s="9"/>
-      <c r="AV1" s="9"/>
-      <c r="AW1" s="9"/>
-      <c r="AX1" s="9"/>
-      <c r="AY1" s="9"/>
-      <c r="AZ1" s="9"/>
-      <c r="BA1" s="9"/>
-      <c r="BB1" s="9"/>
-      <c r="BC1" s="9"/>
-      <c r="BD1" s="9"/>
-      <c r="BE1" s="9"/>
-      <c r="BF1" s="9"/>
-      <c r="BG1" s="9"/>
-      <c r="BH1" s="9"/>
-      <c r="BI1" s="9"/>
-      <c r="BJ1" s="9"/>
-      <c r="BK1" s="9"/>
-      <c r="BL1" s="9"/>
-      <c r="BM1" s="9"/>
-      <c r="BN1" s="9"/>
-      <c r="BO1" s="9"/>
-      <c r="BP1" s="9"/>
-      <c r="BQ1" s="9"/>
-      <c r="BR1" s="9"/>
-      <c r="BS1" s="9"/>
-      <c r="BT1" s="9"/>
-      <c r="BU1" s="9"/>
-      <c r="BV1" s="9"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
+      <c r="AA1" s="2"/>
+      <c r="AB1" s="2"/>
+      <c r="AC1" s="2"/>
+      <c r="AD1" s="2"/>
+      <c r="AE1" s="2"/>
+      <c r="AF1" s="2"/>
+      <c r="AG1" s="2"/>
+      <c r="AH1" s="2"/>
+      <c r="AI1" s="2"/>
+      <c r="AJ1" s="2"/>
+      <c r="AK1" s="2"/>
+      <c r="AL1" s="2"/>
+      <c r="AM1" s="2"/>
+      <c r="AN1" s="2"/>
+      <c r="AO1" s="2"/>
+      <c r="AP1" s="2"/>
+      <c r="AQ1" s="2"/>
+      <c r="AR1" s="2"/>
+      <c r="AS1" s="2"/>
+      <c r="AT1" s="2"/>
+      <c r="AU1" s="2"/>
+      <c r="AV1" s="2"/>
+      <c r="AW1" s="2"/>
+      <c r="AX1" s="2"/>
+      <c r="AY1" s="2"/>
+      <c r="AZ1" s="2"/>
+      <c r="BA1" s="2"/>
+      <c r="BB1" s="2"/>
+      <c r="BC1" s="2"/>
+      <c r="BD1" s="2"/>
+      <c r="BE1" s="2"/>
+      <c r="BF1" s="2"/>
+      <c r="BG1" s="2"/>
+      <c r="BH1" s="2"/>
+      <c r="BI1" s="2"/>
+      <c r="BJ1" s="2"/>
+      <c r="BK1" s="2"/>
+      <c r="BL1" s="2"/>
+      <c r="BM1" s="2"/>
+      <c r="BN1" s="2"/>
+      <c r="BO1" s="2"/>
+      <c r="BP1" s="2"/>
+      <c r="BQ1" s="2"/>
+      <c r="BR1" s="2"/>
+      <c r="BS1" s="2"/>
+      <c r="BT1" s="2"/>
+      <c r="BU1" s="2"/>
+      <c r="BV1" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="9"/>
-      <c r="AB2" s="9"/>
-      <c r="AC2" s="9"/>
-      <c r="AD2" s="9"/>
-      <c r="AE2" s="9"/>
-      <c r="AF2" s="9"/>
-      <c r="AG2" s="9"/>
-      <c r="AH2" s="9"/>
-      <c r="AI2" s="9"/>
-      <c r="AJ2" s="9"/>
-      <c r="AK2" s="9"/>
-      <c r="AL2" s="9"/>
-      <c r="AM2" s="9"/>
-      <c r="AN2" s="9"/>
-      <c r="AO2" s="9"/>
-      <c r="AP2" s="9"/>
-      <c r="AQ2" s="9"/>
-      <c r="AR2" s="9"/>
-      <c r="AS2" s="9"/>
-      <c r="AT2" s="9"/>
-      <c r="AU2" s="9"/>
-      <c r="AV2" s="9"/>
-      <c r="AW2" s="9"/>
-      <c r="AX2" s="9"/>
-      <c r="AY2" s="9"/>
-      <c r="AZ2" s="9"/>
-      <c r="BA2" s="9"/>
-      <c r="BB2" s="9"/>
-      <c r="BC2" s="9"/>
-      <c r="BD2" s="9"/>
-      <c r="BE2" s="9"/>
-      <c r="BF2" s="9"/>
-      <c r="BG2" s="9"/>
-      <c r="BH2" s="9"/>
-      <c r="BI2" s="9"/>
-      <c r="BJ2" s="9"/>
-      <c r="BK2" s="9"/>
-      <c r="BL2" s="9"/>
-      <c r="BM2" s="9"/>
-      <c r="BN2" s="9"/>
-      <c r="BO2" s="9"/>
-      <c r="BP2" s="9"/>
-      <c r="BQ2" s="9"/>
-      <c r="BR2" s="9"/>
-      <c r="BS2" s="9"/>
-      <c r="BT2" s="9"/>
-      <c r="BU2" s="9"/>
-      <c r="BV2" s="9"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="2"/>
+      <c r="AB2" s="2"/>
+      <c r="AC2" s="2"/>
+      <c r="AD2" s="2"/>
+      <c r="AE2" s="2"/>
+      <c r="AF2" s="2"/>
+      <c r="AG2" s="2"/>
+      <c r="AH2" s="2"/>
+      <c r="AI2" s="2"/>
+      <c r="AJ2" s="2"/>
+      <c r="AK2" s="2"/>
+      <c r="AL2" s="2"/>
+      <c r="AM2" s="2"/>
+      <c r="AN2" s="2"/>
+      <c r="AO2" s="2"/>
+      <c r="AP2" s="2"/>
+      <c r="AQ2" s="2"/>
+      <c r="AR2" s="2"/>
+      <c r="AS2" s="2"/>
+      <c r="AT2" s="2"/>
+      <c r="AU2" s="2"/>
+      <c r="AV2" s="2"/>
+      <c r="AW2" s="2"/>
+      <c r="AX2" s="2"/>
+      <c r="AY2" s="2"/>
+      <c r="AZ2" s="2"/>
+      <c r="BA2" s="2"/>
+      <c r="BB2" s="2"/>
+      <c r="BC2" s="2"/>
+      <c r="BD2" s="2"/>
+      <c r="BE2" s="2"/>
+      <c r="BF2" s="2"/>
+      <c r="BG2" s="2"/>
+      <c r="BH2" s="2"/>
+      <c r="BI2" s="2"/>
+      <c r="BJ2" s="2"/>
+      <c r="BK2" s="2"/>
+      <c r="BL2" s="2"/>
+      <c r="BM2" s="2"/>
+      <c r="BN2" s="2"/>
+      <c r="BO2" s="2"/>
+      <c r="BP2" s="2"/>
+      <c r="BQ2" s="2"/>
+      <c r="BR2" s="2"/>
+      <c r="BS2" s="2"/>
+      <c r="BT2" s="2"/>
+      <c r="BU2" s="2"/>
+      <c r="BV2" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="1" t="s">
@@ -2024,27 +2012,27 @@
   <dimension ref="A1:R7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="8.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="8" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="8.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="7" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="7" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="7" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="7" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="7" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="7" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="7" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="7" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="7" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="7" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="7" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="7" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="7" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="7" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="7" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="7" width="9.290714285714287" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2100,7 +2088,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2156,7 +2144,7 @@
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -2212,7 +2200,7 @@
         <v>226</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -2268,7 +2256,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -2324,7 +2312,7 @@
         <v>398</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -2380,25 +2368,25 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="1"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/TEST DATI SAMPLE.xlsx
+++ b/TEST DATI SAMPLE.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="VOLUMI"/>
@@ -725,7 +725,7 @@
     <col min="74" max="74" style="8" width="9.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -803,7 +803,7 @@
       <c r="BU1" s="2"/>
       <c r="BV1" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="20.25">
       <c r="A2" s="1"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -879,7 +879,7 @@
       <c r="BU2" s="2"/>
       <c r="BV2" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="20.25">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -1103,7 +1103,7 @@
         <v>81</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="20.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1327,7 +1327,7 @@
         <v>436</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="20.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="20.25">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -1775,7 +1775,7 @@
         <v>159</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="20.25">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
